--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669406</v>
+        <v>124669410</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473064</v>
+        <v>473092</v>
       </c>
       <c r="R3" t="n">
-        <v>6952895</v>
+        <v>6952891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669403</v>
+        <v>124669411</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473096</v>
+        <v>473091</v>
       </c>
       <c r="R4" t="n">
-        <v>6952927</v>
+        <v>6952891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669412</v>
+        <v>124669406</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473130</v>
+        <v>473064</v>
       </c>
       <c r="R5" t="n">
-        <v>6952845</v>
+        <v>6952895</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669410</v>
+        <v>124669402</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473092</v>
+        <v>473096</v>
       </c>
       <c r="R7" t="n">
-        <v>6952891</v>
+        <v>6952929</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669404</v>
+        <v>124669403</v>
       </c>
       <c r="B8" t="n">
-        <v>98122</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473062</v>
+        <v>473096</v>
       </c>
       <c r="R8" t="n">
-        <v>6952887</v>
+        <v>6952927</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669402</v>
+        <v>124669412</v>
       </c>
       <c r="B9" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473096</v>
+        <v>473130</v>
       </c>
       <c r="R9" t="n">
-        <v>6952929</v>
+        <v>6952845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669411</v>
+        <v>124669407</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>79892</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473091</v>
+        <v>473064</v>
       </c>
       <c r="R10" t="n">
-        <v>6952891</v>
+        <v>6952896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669407</v>
+        <v>124669404</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>98122</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473064</v>
+        <v>473062</v>
       </c>
       <c r="R11" t="n">
-        <v>6952896</v>
+        <v>6952887</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669408</v>
+        <v>124669411</v>
       </c>
       <c r="B2" t="n">
-        <v>79926</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473064</v>
+        <v>473091</v>
       </c>
       <c r="R2" t="n">
-        <v>6952893</v>
+        <v>6952891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669410</v>
+        <v>124669405</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>79920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473092</v>
+        <v>473068</v>
       </c>
       <c r="R3" t="n">
-        <v>6952891</v>
+        <v>6952901</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669411</v>
+        <v>124669408</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>79926</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473091</v>
+        <v>473064</v>
       </c>
       <c r="R4" t="n">
-        <v>6952891</v>
+        <v>6952893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669406</v>
+        <v>124669402</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473064</v>
+        <v>473096</v>
       </c>
       <c r="R5" t="n">
-        <v>6952895</v>
+        <v>6952929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669405</v>
+        <v>124669407</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473068</v>
+        <v>473064</v>
       </c>
       <c r="R6" t="n">
-        <v>6952901</v>
+        <v>6952896</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669402</v>
+        <v>124669410</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473096</v>
+        <v>473092</v>
       </c>
       <c r="R7" t="n">
-        <v>6952929</v>
+        <v>6952891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669403</v>
+        <v>124669412</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473096</v>
+        <v>473130</v>
       </c>
       <c r="R8" t="n">
-        <v>6952927</v>
+        <v>6952845</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669412</v>
+        <v>124669404</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98122</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473130</v>
+        <v>473062</v>
       </c>
       <c r="R9" t="n">
-        <v>6952845</v>
+        <v>6952887</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669407</v>
+        <v>124669406</v>
       </c>
       <c r="B10" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
         <v>473064</v>
       </c>
       <c r="R10" t="n">
-        <v>6952896</v>
+        <v>6952895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669404</v>
+        <v>124669403</v>
       </c>
       <c r="B11" t="n">
-        <v>98122</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473062</v>
+        <v>473096</v>
       </c>
       <c r="R11" t="n">
-        <v>6952887</v>
+        <v>6952927</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669408</v>
+        <v>124669406</v>
       </c>
       <c r="B4" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>473064</v>
       </c>
       <c r="R4" t="n">
-        <v>6952893</v>
+        <v>6952895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669402</v>
+        <v>124669404</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>98122</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473096</v>
+        <v>473062</v>
       </c>
       <c r="R5" t="n">
-        <v>6952929</v>
+        <v>6952887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669407</v>
+        <v>124669402</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473064</v>
+        <v>473096</v>
       </c>
       <c r="R6" t="n">
-        <v>6952896</v>
+        <v>6952929</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669410</v>
+        <v>124669407</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>79892</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473092</v>
+        <v>473064</v>
       </c>
       <c r="R7" t="n">
-        <v>6952891</v>
+        <v>6952896</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669412</v>
+        <v>124669410</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473130</v>
+        <v>473092</v>
       </c>
       <c r="R8" t="n">
-        <v>6952845</v>
+        <v>6952891</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669404</v>
+        <v>124669403</v>
       </c>
       <c r="B9" t="n">
-        <v>98122</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473062</v>
+        <v>473096</v>
       </c>
       <c r="R9" t="n">
-        <v>6952887</v>
+        <v>6952927</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669406</v>
+        <v>124669412</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473064</v>
+        <v>473130</v>
       </c>
       <c r="R10" t="n">
-        <v>6952895</v>
+        <v>6952845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669403</v>
+        <v>124669408</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473096</v>
+        <v>473064</v>
       </c>
       <c r="R11" t="n">
-        <v>6952927</v>
+        <v>6952893</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669411</v>
+        <v>124669410</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473091</v>
+        <v>473092</v>
       </c>
       <c r="R2" t="n">
         <v>6952891</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669406</v>
+        <v>124669408</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>473064</v>
       </c>
       <c r="R4" t="n">
-        <v>6952895</v>
+        <v>6952893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669404</v>
+        <v>124669403</v>
       </c>
       <c r="B5" t="n">
-        <v>98122</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473062</v>
+        <v>473096</v>
       </c>
       <c r="R5" t="n">
-        <v>6952887</v>
+        <v>6952927</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669402</v>
+        <v>124669412</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473096</v>
+        <v>473130</v>
       </c>
       <c r="R6" t="n">
-        <v>6952929</v>
+        <v>6952845</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669407</v>
+        <v>124669404</v>
       </c>
       <c r="B7" t="n">
-        <v>79892</v>
+        <v>98122</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473064</v>
+        <v>473062</v>
       </c>
       <c r="R7" t="n">
-        <v>6952896</v>
+        <v>6952887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669410</v>
+        <v>124669407</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>79892</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473092</v>
+        <v>473064</v>
       </c>
       <c r="R8" t="n">
-        <v>6952891</v>
+        <v>6952896</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669403</v>
+        <v>124669402</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>473096</v>
       </c>
       <c r="R9" t="n">
-        <v>6952927</v>
+        <v>6952929</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669412</v>
+        <v>124669406</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473130</v>
+        <v>473064</v>
       </c>
       <c r="R10" t="n">
-        <v>6952845</v>
+        <v>6952895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669408</v>
+        <v>124669411</v>
       </c>
       <c r="B11" t="n">
-        <v>79926</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473064</v>
+        <v>473091</v>
       </c>
       <c r="R11" t="n">
-        <v>6952893</v>
+        <v>6952891</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669410</v>
+        <v>124669411</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473092</v>
+        <v>473091</v>
       </c>
       <c r="R2" t="n">
         <v>6952891</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669405</v>
+        <v>124669403</v>
       </c>
       <c r="B3" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473068</v>
+        <v>473096</v>
       </c>
       <c r="R3" t="n">
-        <v>6952901</v>
+        <v>6952927</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669408</v>
+        <v>124669402</v>
       </c>
       <c r="B4" t="n">
-        <v>79926</v>
+        <v>79920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473064</v>
+        <v>473096</v>
       </c>
       <c r="R4" t="n">
-        <v>6952893</v>
+        <v>6952929</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669403</v>
+        <v>124669410</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473096</v>
+        <v>473092</v>
       </c>
       <c r="R5" t="n">
-        <v>6952927</v>
+        <v>6952891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669412</v>
+        <v>124669404</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98122</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473130</v>
+        <v>473062</v>
       </c>
       <c r="R6" t="n">
-        <v>6952845</v>
+        <v>6952887</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669404</v>
+        <v>124669408</v>
       </c>
       <c r="B7" t="n">
-        <v>98122</v>
+        <v>79926</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473062</v>
+        <v>473064</v>
       </c>
       <c r="R7" t="n">
-        <v>6952887</v>
+        <v>6952893</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669402</v>
+        <v>124669412</v>
       </c>
       <c r="B9" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473096</v>
+        <v>473130</v>
       </c>
       <c r="R9" t="n">
-        <v>6952929</v>
+        <v>6952845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669406</v>
+        <v>124669405</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473064</v>
+        <v>473068</v>
       </c>
       <c r="R10" t="n">
-        <v>6952895</v>
+        <v>6952901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669411</v>
+        <v>124669406</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473091</v>
+        <v>473064</v>
       </c>
       <c r="R11" t="n">
-        <v>6952891</v>
+        <v>6952895</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669403</v>
+        <v>124669402</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,7 +820,7 @@
         <v>473096</v>
       </c>
       <c r="R3" t="n">
-        <v>6952927</v>
+        <v>6952929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669402</v>
+        <v>124669403</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>473096</v>
       </c>
       <c r="R4" t="n">
-        <v>6952929</v>
+        <v>6952927</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669402</v>
+        <v>124669404</v>
       </c>
       <c r="B3" t="n">
-        <v>79920</v>
+        <v>98122</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473096</v>
+        <v>473062</v>
       </c>
       <c r="R3" t="n">
-        <v>6952929</v>
+        <v>6952887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669404</v>
+        <v>124669402</v>
       </c>
       <c r="B6" t="n">
-        <v>98122</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473062</v>
+        <v>473096</v>
       </c>
       <c r="R6" t="n">
-        <v>6952887</v>
+        <v>6952929</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669408</v>
+        <v>124669407</v>
       </c>
       <c r="B7" t="n">
-        <v>79926</v>
+        <v>79892</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
         <v>473064</v>
       </c>
       <c r="R7" t="n">
-        <v>6952893</v>
+        <v>6952896</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669407</v>
+        <v>124669408</v>
       </c>
       <c r="B8" t="n">
-        <v>79892</v>
+        <v>79926</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
         <v>473064</v>
       </c>
       <c r="R8" t="n">
-        <v>6952896</v>
+        <v>6952893</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669412</v>
+        <v>124669405</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473130</v>
+        <v>473068</v>
       </c>
       <c r="R9" t="n">
-        <v>6952845</v>
+        <v>6952901</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669405</v>
+        <v>124669412</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473068</v>
+        <v>473130</v>
       </c>
       <c r="R10" t="n">
-        <v>6952901</v>
+        <v>6952845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669411</v>
+        <v>124669405</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473091</v>
+        <v>473068</v>
       </c>
       <c r="R2" t="n">
-        <v>6952891</v>
+        <v>6952901</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669404</v>
+        <v>124669406</v>
       </c>
       <c r="B3" t="n">
-        <v>98122</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473062</v>
+        <v>473064</v>
       </c>
       <c r="R3" t="n">
-        <v>6952887</v>
+        <v>6952895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669403</v>
+        <v>124669404</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>98122</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473096</v>
+        <v>473062</v>
       </c>
       <c r="R4" t="n">
-        <v>6952927</v>
+        <v>6952887</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669402</v>
+        <v>124669403</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
         <v>473096</v>
       </c>
       <c r="R6" t="n">
-        <v>6952929</v>
+        <v>6952927</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669407</v>
+        <v>124669412</v>
       </c>
       <c r="B7" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473064</v>
+        <v>473130</v>
       </c>
       <c r="R7" t="n">
-        <v>6952896</v>
+        <v>6952845</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669408</v>
+        <v>124669411</v>
       </c>
       <c r="B8" t="n">
-        <v>79926</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473064</v>
+        <v>473091</v>
       </c>
       <c r="R8" t="n">
-        <v>6952893</v>
+        <v>6952891</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669405</v>
+        <v>124669407</v>
       </c>
       <c r="B9" t="n">
-        <v>79920</v>
+        <v>79892</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473068</v>
+        <v>473064</v>
       </c>
       <c r="R9" t="n">
-        <v>6952901</v>
+        <v>6952896</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669412</v>
+        <v>124669408</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,20 +1503,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473130</v>
+        <v>473064</v>
       </c>
       <c r="R10" t="n">
-        <v>6952845</v>
+        <v>6952893</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669406</v>
+        <v>124669402</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473064</v>
+        <v>473096</v>
       </c>
       <c r="R11" t="n">
-        <v>6952895</v>
+        <v>6952929</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669406</v>
+        <v>124669412</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473064</v>
+        <v>473130</v>
       </c>
       <c r="R3" t="n">
-        <v>6952895</v>
+        <v>6952845</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669404</v>
+        <v>124669408</v>
       </c>
       <c r="B4" t="n">
-        <v>98122</v>
+        <v>79926</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473062</v>
+        <v>473064</v>
       </c>
       <c r="R4" t="n">
-        <v>6952887</v>
+        <v>6952893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669410</v>
+        <v>124669407</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>79892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473092</v>
+        <v>473064</v>
       </c>
       <c r="R5" t="n">
-        <v>6952891</v>
+        <v>6952896</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669403</v>
+        <v>124669404</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>98122</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473096</v>
+        <v>473062</v>
       </c>
       <c r="R6" t="n">
-        <v>6952927</v>
+        <v>6952887</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669412</v>
+        <v>124669410</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473130</v>
+        <v>473092</v>
       </c>
       <c r="R7" t="n">
-        <v>6952845</v>
+        <v>6952891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669411</v>
+        <v>124669406</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473091</v>
+        <v>473064</v>
       </c>
       <c r="R8" t="n">
-        <v>6952891</v>
+        <v>6952895</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669407</v>
+        <v>124669403</v>
       </c>
       <c r="B9" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473064</v>
+        <v>473096</v>
       </c>
       <c r="R9" t="n">
-        <v>6952896</v>
+        <v>6952927</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669408</v>
+        <v>124669402</v>
       </c>
       <c r="B10" t="n">
-        <v>79926</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473064</v>
+        <v>473096</v>
       </c>
       <c r="R10" t="n">
-        <v>6952893</v>
+        <v>6952929</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669402</v>
+        <v>124669411</v>
       </c>
       <c r="B11" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473096</v>
+        <v>473091</v>
       </c>
       <c r="R11" t="n">
-        <v>6952929</v>
+        <v>6952891</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669405</v>
+        <v>124669404</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>98122</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473068</v>
+        <v>473062</v>
       </c>
       <c r="R2" t="n">
-        <v>6952901</v>
+        <v>6952887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669412</v>
+        <v>124669411</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473130</v>
+        <v>473091</v>
       </c>
       <c r="R3" t="n">
-        <v>6952845</v>
+        <v>6952891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669408</v>
+        <v>124669410</v>
       </c>
       <c r="B4" t="n">
-        <v>79926</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473064</v>
+        <v>473092</v>
       </c>
       <c r="R4" t="n">
-        <v>6952893</v>
+        <v>6952891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669407</v>
+        <v>124669405</v>
       </c>
       <c r="B5" t="n">
-        <v>79892</v>
+        <v>79920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473064</v>
+        <v>473068</v>
       </c>
       <c r="R5" t="n">
-        <v>6952896</v>
+        <v>6952901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669404</v>
+        <v>124669403</v>
       </c>
       <c r="B6" t="n">
-        <v>98122</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473062</v>
+        <v>473096</v>
       </c>
       <c r="R6" t="n">
-        <v>6952887</v>
+        <v>6952927</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669410</v>
+        <v>124669412</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473092</v>
+        <v>473130</v>
       </c>
       <c r="R7" t="n">
-        <v>6952891</v>
+        <v>6952845</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669406</v>
+        <v>124669408</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
         <v>473064</v>
       </c>
       <c r="R8" t="n">
-        <v>6952895</v>
+        <v>6952893</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669403</v>
+        <v>124669406</v>
       </c>
       <c r="B9" t="n">
         <v>79891</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473096</v>
+        <v>473064</v>
       </c>
       <c r="R9" t="n">
-        <v>6952927</v>
+        <v>6952895</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669402</v>
+        <v>124669407</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>79892</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473096</v>
+        <v>473064</v>
       </c>
       <c r="R10" t="n">
-        <v>6952929</v>
+        <v>6952896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669411</v>
+        <v>124669402</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473091</v>
+        <v>473096</v>
       </c>
       <c r="R11" t="n">
-        <v>6952891</v>
+        <v>6952929</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669404</v>
+        <v>124669411</v>
       </c>
       <c r="B2" t="n">
-        <v>98122</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473062</v>
+        <v>473091</v>
       </c>
       <c r="R2" t="n">
-        <v>6952887</v>
+        <v>6952891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669411</v>
+        <v>124669404</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>98122</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473091</v>
+        <v>473062</v>
       </c>
       <c r="R3" t="n">
-        <v>6952891</v>
+        <v>6952887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669410</v>
+        <v>124669406</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473092</v>
+        <v>473064</v>
       </c>
       <c r="R4" t="n">
-        <v>6952891</v>
+        <v>6952895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669405</v>
+        <v>124669410</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473068</v>
+        <v>473092</v>
       </c>
       <c r="R5" t="n">
-        <v>6952901</v>
+        <v>6952891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669403</v>
+        <v>124669407</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473096</v>
+        <v>473064</v>
       </c>
       <c r="R6" t="n">
-        <v>6952927</v>
+        <v>6952896</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669408</v>
+        <v>124669405</v>
       </c>
       <c r="B8" t="n">
-        <v>79926</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473064</v>
+        <v>473068</v>
       </c>
       <c r="R8" t="n">
-        <v>6952893</v>
+        <v>6952901</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669406</v>
+        <v>124669402</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473064</v>
+        <v>473096</v>
       </c>
       <c r="R9" t="n">
-        <v>6952895</v>
+        <v>6952929</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669407</v>
+        <v>124669408</v>
       </c>
       <c r="B10" t="n">
-        <v>79892</v>
+        <v>79926</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
         <v>473064</v>
       </c>
       <c r="R10" t="n">
-        <v>6952896</v>
+        <v>6952893</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669402</v>
+        <v>124669403</v>
       </c>
       <c r="B11" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
         <v>473096</v>
       </c>
       <c r="R11" t="n">
-        <v>6952929</v>
+        <v>6952927</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669411</v>
+        <v>124669404</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>98122</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473091</v>
+        <v>473062</v>
       </c>
       <c r="R2" t="n">
-        <v>6952891</v>
+        <v>6952887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669404</v>
+        <v>124669408</v>
       </c>
       <c r="B3" t="n">
-        <v>98122</v>
+        <v>79926</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473062</v>
+        <v>473064</v>
       </c>
       <c r="R3" t="n">
-        <v>6952887</v>
+        <v>6952893</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669406</v>
+        <v>124669405</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473064</v>
+        <v>473068</v>
       </c>
       <c r="R4" t="n">
-        <v>6952895</v>
+        <v>6952901</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669407</v>
+        <v>124669406</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
         <v>473064</v>
       </c>
       <c r="R6" t="n">
-        <v>6952896</v>
+        <v>6952895</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669405</v>
+        <v>124669402</v>
       </c>
       <c r="B8" t="n">
         <v>79920</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473068</v>
+        <v>473096</v>
       </c>
       <c r="R8" t="n">
-        <v>6952901</v>
+        <v>6952929</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669402</v>
+        <v>124669403</v>
       </c>
       <c r="B9" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>473096</v>
       </c>
       <c r="R9" t="n">
-        <v>6952929</v>
+        <v>6952927</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669408</v>
+        <v>124669407</v>
       </c>
       <c r="B10" t="n">
-        <v>79926</v>
+        <v>79892</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
         <v>473064</v>
       </c>
       <c r="R10" t="n">
-        <v>6952893</v>
+        <v>6952896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669403</v>
+        <v>124669411</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473096</v>
+        <v>473091</v>
       </c>
       <c r="R11" t="n">
-        <v>6952927</v>
+        <v>6952891</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669404</v>
+        <v>124669410</v>
       </c>
       <c r="B2" t="n">
-        <v>98122</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473062</v>
+        <v>473092</v>
       </c>
       <c r="R2" t="n">
-        <v>6952887</v>
+        <v>6952891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669405</v>
+        <v>124669402</v>
       </c>
       <c r="B4" t="n">
         <v>79920</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473068</v>
+        <v>473096</v>
       </c>
       <c r="R4" t="n">
-        <v>6952901</v>
+        <v>6952929</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669410</v>
+        <v>124669404</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>98122</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473092</v>
+        <v>473062</v>
       </c>
       <c r="R5" t="n">
-        <v>6952891</v>
+        <v>6952887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669406</v>
+        <v>124669407</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
         <v>473064</v>
       </c>
       <c r="R6" t="n">
-        <v>6952895</v>
+        <v>6952896</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669412</v>
+        <v>124669405</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473130</v>
+        <v>473068</v>
       </c>
       <c r="R7" t="n">
-        <v>6952845</v>
+        <v>6952901</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669402</v>
+        <v>124669406</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473096</v>
+        <v>473064</v>
       </c>
       <c r="R8" t="n">
-        <v>6952929</v>
+        <v>6952895</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669403</v>
+        <v>124669411</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473096</v>
+        <v>473091</v>
       </c>
       <c r="R9" t="n">
-        <v>6952927</v>
+        <v>6952891</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669407</v>
+        <v>124669412</v>
       </c>
       <c r="B10" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473064</v>
+        <v>473130</v>
       </c>
       <c r="R10" t="n">
-        <v>6952896</v>
+        <v>6952845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669411</v>
+        <v>124669403</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473091</v>
+        <v>473096</v>
       </c>
       <c r="R11" t="n">
-        <v>6952891</v>
+        <v>6952927</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669410</v>
+        <v>124669404</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>98122</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473092</v>
+        <v>473062</v>
       </c>
       <c r="R2" t="n">
-        <v>6952891</v>
+        <v>6952887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669402</v>
+        <v>124669410</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473096</v>
+        <v>473092</v>
       </c>
       <c r="R4" t="n">
-        <v>6952929</v>
+        <v>6952891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669404</v>
+        <v>124669407</v>
       </c>
       <c r="B5" t="n">
-        <v>98122</v>
+        <v>79892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473062</v>
+        <v>473064</v>
       </c>
       <c r="R5" t="n">
-        <v>6952887</v>
+        <v>6952896</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669407</v>
+        <v>124669403</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473064</v>
+        <v>473096</v>
       </c>
       <c r="R6" t="n">
-        <v>6952896</v>
+        <v>6952927</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669405</v>
+        <v>124669411</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473068</v>
+        <v>473091</v>
       </c>
       <c r="R7" t="n">
-        <v>6952901</v>
+        <v>6952891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669406</v>
+        <v>124669405</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473064</v>
+        <v>473068</v>
       </c>
       <c r="R8" t="n">
-        <v>6952895</v>
+        <v>6952901</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669411</v>
+        <v>124669402</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473091</v>
+        <v>473096</v>
       </c>
       <c r="R9" t="n">
-        <v>6952891</v>
+        <v>6952929</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669412</v>
+        <v>124669406</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473130</v>
+        <v>473064</v>
       </c>
       <c r="R10" t="n">
-        <v>6952845</v>
+        <v>6952895</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669403</v>
+        <v>124669412</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473096</v>
+        <v>473130</v>
       </c>
       <c r="R11" t="n">
-        <v>6952927</v>
+        <v>6952845</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669404</v>
+        <v>124669402</v>
       </c>
       <c r="B2" t="n">
-        <v>98122</v>
+        <v>79920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473062</v>
+        <v>473096</v>
       </c>
       <c r="R2" t="n">
-        <v>6952887</v>
+        <v>6952929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669408</v>
+        <v>124669411</v>
       </c>
       <c r="B3" t="n">
-        <v>79926</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473064</v>
+        <v>473091</v>
       </c>
       <c r="R3" t="n">
-        <v>6952893</v>
+        <v>6952891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669410</v>
+        <v>124669403</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473092</v>
+        <v>473096</v>
       </c>
       <c r="R4" t="n">
-        <v>6952891</v>
+        <v>6952927</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669403</v>
+        <v>124669410</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473096</v>
+        <v>473092</v>
       </c>
       <c r="R6" t="n">
-        <v>6952927</v>
+        <v>6952891</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669411</v>
+        <v>124669406</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473091</v>
+        <v>473064</v>
       </c>
       <c r="R7" t="n">
-        <v>6952891</v>
+        <v>6952895</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669405</v>
+        <v>124669408</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>79926</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473068</v>
+        <v>473064</v>
       </c>
       <c r="R8" t="n">
-        <v>6952901</v>
+        <v>6952893</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669402</v>
+        <v>124669404</v>
       </c>
       <c r="B9" t="n">
-        <v>79920</v>
+        <v>98122</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473096</v>
+        <v>473062</v>
       </c>
       <c r="R9" t="n">
-        <v>6952929</v>
+        <v>6952887</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669406</v>
+        <v>124669405</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473064</v>
+        <v>473068</v>
       </c>
       <c r="R10" t="n">
-        <v>6952895</v>
+        <v>6952901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669402</v>
+        <v>124669408</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>79926</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473096</v>
+        <v>473064</v>
       </c>
       <c r="R2" t="n">
-        <v>6952929</v>
+        <v>6952893</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669411</v>
+        <v>124669403</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473091</v>
+        <v>473096</v>
       </c>
       <c r="R3" t="n">
-        <v>6952891</v>
+        <v>6952927</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669403</v>
+        <v>124669405</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473096</v>
+        <v>473068</v>
       </c>
       <c r="R4" t="n">
-        <v>6952927</v>
+        <v>6952901</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669407</v>
+        <v>124669404</v>
       </c>
       <c r="B5" t="n">
-        <v>79892</v>
+        <v>98122</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473064</v>
+        <v>473062</v>
       </c>
       <c r="R5" t="n">
-        <v>6952896</v>
+        <v>6952887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669410</v>
+        <v>124669411</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473092</v>
+        <v>473091</v>
       </c>
       <c r="R6" t="n">
         <v>6952891</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669406</v>
+        <v>124669410</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473064</v>
+        <v>473092</v>
       </c>
       <c r="R7" t="n">
-        <v>6952895</v>
+        <v>6952891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669408</v>
+        <v>124669406</v>
       </c>
       <c r="B8" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
         <v>473064</v>
       </c>
       <c r="R8" t="n">
-        <v>6952893</v>
+        <v>6952895</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669404</v>
+        <v>124669412</v>
       </c>
       <c r="B9" t="n">
-        <v>98122</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473062</v>
+        <v>473130</v>
       </c>
       <c r="R9" t="n">
-        <v>6952887</v>
+        <v>6952845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669405</v>
+        <v>124669402</v>
       </c>
       <c r="B10" t="n">
         <v>79920</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473068</v>
+        <v>473096</v>
       </c>
       <c r="R10" t="n">
-        <v>6952901</v>
+        <v>6952929</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669412</v>
+        <v>124669407</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473130</v>
+        <v>473064</v>
       </c>
       <c r="R11" t="n">
-        <v>6952845</v>
+        <v>6952896</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669402</v>
+        <v>124669407</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>79892</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473096</v>
+        <v>473064</v>
       </c>
       <c r="R10" t="n">
-        <v>6952929</v>
+        <v>6952896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669407</v>
+        <v>124669402</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>79920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473064</v>
+        <v>473096</v>
       </c>
       <c r="R11" t="n">
-        <v>6952896</v>
+        <v>6952929</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669408</v>
+        <v>124669407</v>
       </c>
       <c r="B2" t="n">
-        <v>79926</v>
+        <v>79892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,7 +718,7 @@
         <v>473064</v>
       </c>
       <c r="R2" t="n">
-        <v>6952893</v>
+        <v>6952896</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669403</v>
+        <v>124669412</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473096</v>
+        <v>473130</v>
       </c>
       <c r="R3" t="n">
-        <v>6952927</v>
+        <v>6952845</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669405</v>
+        <v>124669408</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>79926</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473068</v>
+        <v>473064</v>
       </c>
       <c r="R4" t="n">
-        <v>6952901</v>
+        <v>6952893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669404</v>
+        <v>124669411</v>
       </c>
       <c r="B5" t="n">
-        <v>98122</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473062</v>
+        <v>473091</v>
       </c>
       <c r="R5" t="n">
-        <v>6952887</v>
+        <v>6952891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669411</v>
+        <v>124669404</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>98122</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473091</v>
+        <v>473062</v>
       </c>
       <c r="R6" t="n">
-        <v>6952891</v>
+        <v>6952887</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669410</v>
+        <v>124669402</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473092</v>
+        <v>473096</v>
       </c>
       <c r="R7" t="n">
-        <v>6952891</v>
+        <v>6952929</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669412</v>
+        <v>124669410</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473130</v>
+        <v>473092</v>
       </c>
       <c r="R9" t="n">
-        <v>6952845</v>
+        <v>6952891</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669407</v>
+        <v>124669405</v>
       </c>
       <c r="B10" t="n">
-        <v>79892</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473064</v>
+        <v>473068</v>
       </c>
       <c r="R10" t="n">
-        <v>6952896</v>
+        <v>6952901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669402</v>
+        <v>124669403</v>
       </c>
       <c r="B11" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
         <v>473096</v>
       </c>
       <c r="R11" t="n">
-        <v>6952929</v>
+        <v>6952927</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35893-2024 artfynd.xlsx
+++ b/artfynd/A 35893-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124669407</v>
+        <v>124669405</v>
       </c>
       <c r="B2" t="n">
-        <v>79892</v>
+        <v>80057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473064</v>
+        <v>473068</v>
       </c>
       <c r="R2" t="n">
-        <v>6952896</v>
+        <v>6952901</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124669412</v>
+        <v>124669411</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473130</v>
+        <v>473091</v>
       </c>
       <c r="R3" t="n">
-        <v>6952845</v>
+        <v>6952891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124669408</v>
+        <v>124669410</v>
       </c>
       <c r="B4" t="n">
-        <v>79926</v>
+        <v>91459</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473064</v>
+        <v>473092</v>
       </c>
       <c r="R4" t="n">
-        <v>6952893</v>
+        <v>6952891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124669411</v>
+        <v>124669402</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>80057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473091</v>
+        <v>473096</v>
       </c>
       <c r="R5" t="n">
-        <v>6952891</v>
+        <v>6952929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124669404</v>
+        <v>124669406</v>
       </c>
       <c r="B6" t="n">
-        <v>98122</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473062</v>
+        <v>473064</v>
       </c>
       <c r="R6" t="n">
-        <v>6952887</v>
+        <v>6952895</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124669402</v>
+        <v>124669404</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>98290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473096</v>
+        <v>473062</v>
       </c>
       <c r="R7" t="n">
-        <v>6952929</v>
+        <v>6952887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124669406</v>
+        <v>124669407</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>80029</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
         <v>473064</v>
       </c>
       <c r="R8" t="n">
-        <v>6952895</v>
+        <v>6952896</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124669410</v>
+        <v>124669403</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>80028</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473092</v>
+        <v>473096</v>
       </c>
       <c r="R9" t="n">
-        <v>6952891</v>
+        <v>6952927</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124669405</v>
+        <v>124669412</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473068</v>
+        <v>473130</v>
       </c>
       <c r="R10" t="n">
-        <v>6952901</v>
+        <v>6952845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124669403</v>
+        <v>124669408</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>80063</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473096</v>
+        <v>473064</v>
       </c>
       <c r="R11" t="n">
-        <v>6952927</v>
+        <v>6952893</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
